--- a/Pre-week-2/homework2.xlsx
+++ b/Pre-week-2/homework2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dimit\Documents\DataAnalytics\Pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A1009D-909B-409E-A27D-9680AC706514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE67F5F6-C33C-4DCC-A54B-1390D973E4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{D943E52C-D0F6-4AEA-B91E-E48A7EB72FFE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D943E52C-D0F6-4AEA-B91E-E48A7EB72FFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Store_Data" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
   <si>
     <t>Store A</t>
   </si>
@@ -119,9 +119,6 @@
   </si>
   <si>
     <t>Categorical Columns= Regien / Category</t>
-  </si>
-  <si>
-    <t>Row Labels</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -169,6 +166,12 @@
   </si>
   <si>
     <t>The chart clearly shows that Electronics is the top-performing category, while Home Goods underperforms compared to the others.</t>
+  </si>
+  <si>
+    <t>Regions</t>
+  </si>
+  <si>
+    <t>Categories</t>
   </si>
 </sst>
 </file>
@@ -2570,7 +2573,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4995A2FD-821D-41EF-AAFC-0CE4E345090E}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4995A2FD-821D-41EF-AAFC-0CE4E345090E}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Categories">
   <location ref="I4:J9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -2636,7 +2639,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F9E82D4B-C6D3-4E33-BD16-B28900024C1A}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F9E82D4B-C6D3-4E33-BD16-B28900024C1A}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Regions">
   <location ref="A18:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0">
@@ -3115,10 +3118,10 @@
         <v>51</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -3215,7 +3218,7 @@
         <v>46</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J9" s="6">
         <v>593</v>
@@ -3282,10 +3285,10 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
@@ -3322,7 +3325,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" s="6">
         <v>593</v>
@@ -3347,18 +3350,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3376,26 +3379,26 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
